--- a/docs/РЫНОК 3.0.0 — карты целиком.xlsx
+++ b/docs/РЫНОК 3.0.0 — карты целиком.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Рынок 3.0.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рынок 3.0.0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Рынок 3.0.0'!$A$1:$H$10</definedName>

--- a/docs/РЫНОК 3.0.0 — карты целиком.xlsx
+++ b/docs/РЫНОК 3.0.0 — карты целиком.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Рынок 3.0.0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Предложения — сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Разрезы" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Рынок 3.0.0'!$A$1:$H$10</definedName>
@@ -39,7 +41,7 @@
       <color rgb="FFB06000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3C3160"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -113,6 +120,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -892,4 +905,1040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>№ карты</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>карта</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>финиш</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>сторона</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>предложение</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Подстанция</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr"/>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>ПОДКЛЮЧЕНИЕ: келемий ИЗ ОБЩЕГО ЗАПАСА встаёт на ячейку энергии твоего здания навсегда</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>энергия</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Подстанция</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>ПЕРЕКЛЮЧЕНИЕ: свободное действие Смена энергии</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>свободное действие</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>энергия</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Оружейный склад</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>ПОГРУЗКА: 4 боеприпаса</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>ресурс</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>боеприпас</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Оружейный склад</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>ТРЕВОГА: свободное действие Бой и 1 боеприпас</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>свободное действие</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>боеприпас</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Биржа труда</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>ПОДРЯД: свободное действие Стройка и 2 монеты</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>свободное действие</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>операции стройки</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Биржа труда</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>СУБСИДИЯ: 6 монет</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>ресурс</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>операции стройки</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Штабная сводка</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>ПЕРЕХВАТ: забери жетон первого игрока И 1 карту задания с руки того же игрока</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>очерёдность</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>очерёдность</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Штабная сводка</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>РАЗНАРЯДКА: 4 карты заданий, оставь 2</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>карты заданий</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>очерёдность</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Ремонтные мастерские</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr"/>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>РЕМОНТ: сними весь урон со всех своих жетонов на ДВУХ своих гексах</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>живучесть</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Ремонтные мастерские</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>СБОР: собери любые свои войска с поля на один гекс</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>живучесть</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Технический совет</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>ГРАНТ: выполни действие Наука так, будто трофеев у тебя на 1 больше</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>ресурс</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>треки науки</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Технический совет</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>ФИНИШ</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>СУБСИДИЯ: 3 трофея</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>ресурс</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>треки науки</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Земельный комитет</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr"/>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>РЕНОВАЦИЯ: замени на поле нейтральным чужое здание (его — в запас владельцу)</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>позиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Земельный комитет</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>ОТВОД: перенеси до двух своих зданий на любые гексы</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>позиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Чёрный рынок</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr"/>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>ПРОЕКТ: тяни 1 карту супер-задания вслепую</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>карта в личную зону</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>супер-слой</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Чёрный рынок</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>ПОСТАВКА: тяни 1 карту супер-арсенала вслепую</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>карта в личную зону</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>супер-слой</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Литейный двор</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr"/>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>левое</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>ОТЛИВКА: свободное действие Сборка</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>свободное действие</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>производство</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Литейный двор</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>правое</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>ПЕРЕПЛАВКА: 1 трофей ИЛИ уничтоженный жетон → 2 боеприпаса</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>размен</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>производство</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>разрез</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>значение</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>предложений</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>номера карт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>работа по полю</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>1, 5, 5, 7, 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>свободное действие</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>ресурс</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>2, 3, 6, 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>карта в личную зону</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>8, 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>очерёдность</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>карты заданий</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>род эффекта</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>размен</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>энергия</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>боеприпас</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>операции стройки</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>очерёдность</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>живучесть</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>треки науки</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>позиция</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>супер-слой</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>нехватка</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>производство</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>флажок ФИНИША</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>карт с флажком</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>2, 4, 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>